--- a/data/02_Daily_Sheets/Expressions_2026-06-03.xlsx
+++ b/data/02_Daily_Sheets/Expressions_2026-06-03.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CHI-20260603-001</t>
+          <t>CHI-20260603-005</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -481,173 +481,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>深耕</t>
+          <t>用人单位</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>Noun</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>shēn gēng</t>
+          <t>yòngrén dānwèi</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>깊이 경작하다, 심층적으로 파고들다 (비유적으로)</t>
+          <t>고용주, 사용자 (회사, 기관 등)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>北京多所学校深耕健...</t>
+          <t>用人单位未签订劳动合同、未缴纳工伤保险，员工因工死亡后，单位直接否认劳动关系，拒绝支付任何赔偿，甚至失联跑路。</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>这家公司在人工智能领域深耕多年，积累了丰富的经验。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CHI-20260603-002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Scraped_News</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>践行</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Verb</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>jiàn xíng</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>실천하다; 이행하다</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>践行志愿服务...</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>我们应该在日常工作中践行公司的核心价值观。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CHI-20260603-003</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Scraped_News</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>抱团</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Colloquialism</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>bàotuán</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>뭉치다, 단결하다 (서로 돕기 위해)</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>麻江教育“抱团记”.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>面对激烈的市场竞争，小公司更需要抱团取暖，共同发展。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>CHI-20260603-004</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Scraped_News</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>扫码添加</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Verb phrase</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>sǎomǎ tiānjiā</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>QR 코드를 스캔하여 추가하다</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>为获取密码“扫码添加...</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>你可以扫码添加我的微信，方便以后联系。</t>
+          <t>在入职前，一定要仔细了解用人单位的规章制度。</t>
         </is>
       </c>
     </row>

--- a/data/02_Daily_Sheets/Expressions_2026-06-03.xlsx
+++ b/data/02_Daily_Sheets/Expressions_2026-06-03.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CHI-20260603-005</t>
+          <t>CHI-20260603-006</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -481,32 +481,79 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>用人单位</t>
+          <t>签订劳动合同</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Noun</t>
+          <t>Separable Verb Phrase</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>yòngrén dānwèi</t>
+          <t>qiāndìng láodòng hétong</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>고용주, 사용자 (회사, 기관 등)</t>
+          <t>근로 계약을 체결하다</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>用人单位未签订劳动合同、未缴纳工伤保险，员工因工死亡后，单位直接否认劳动关系，拒绝支付任何赔偿，甚至失联跑路。</t>
+          <t>用人单位未签订劳动合同、未缴纳工伤保险...</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>在入职前，一定要仔细了解用人单位的规章制度。</t>
+          <t>新员工入职前，必须先签订劳动合同，明确双方的权利义务。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CHI-20260603-007</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Scraped_News</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>作证据</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Verb phrase</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>zuò zhèng jù</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>증거로 삼다, 증거가 되다</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>“AI生成照片”作证据？</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>你的证词可以作证据提交给警方。</t>
         </is>
       </c>
     </row>
